--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930307</v>
+        <v>129930311</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747938</v>
+        <v>748018</v>
       </c>
       <c r="R3" t="n">
-        <v>7304142</v>
+        <v>7304181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930311</v>
+        <v>129930307</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748018</v>
+        <v>747938</v>
       </c>
       <c r="R4" t="n">
-        <v>7304181</v>
+        <v>7304142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129930300</v>
       </c>
       <c r="B5" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129930306</v>
       </c>
       <c r="B6" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129930308</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129930312</v>
       </c>
       <c r="B10" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129930302</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129930310</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129930304</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930311</v>
+        <v>129930307</v>
       </c>
       <c r="B3" t="n">
-        <v>80218</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748018</v>
+        <v>747938</v>
       </c>
       <c r="R3" t="n">
-        <v>7304181</v>
+        <v>7304142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930307</v>
+        <v>129930311</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747938</v>
+        <v>748018</v>
       </c>
       <c r="R4" t="n">
-        <v>7304142</v>
+        <v>7304181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129930307</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129930311</v>
       </c>
       <c r="B4" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129930300</v>
+        <v>129930306</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>80096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748211</v>
+        <v>747971</v>
       </c>
       <c r="R5" t="n">
-        <v>7303986</v>
+        <v>7304141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129930306</v>
+        <v>129930300</v>
       </c>
       <c r="B6" t="n">
-        <v>80093</v>
+        <v>80221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747971</v>
+        <v>748211</v>
       </c>
       <c r="R6" t="n">
-        <v>7304141</v>
+        <v>7303986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129930308</v>
       </c>
       <c r="B7" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129930312</v>
       </c>
       <c r="B10" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129930302</v>
       </c>
       <c r="B11" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129930310</v>
       </c>
       <c r="B12" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129930304</v>
       </c>
       <c r="B13" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129930307</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129930311</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129930306</v>
+        <v>129930300</v>
       </c>
       <c r="B5" t="n">
-        <v>80096</v>
+        <v>80222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747971</v>
+        <v>748211</v>
       </c>
       <c r="R5" t="n">
-        <v>7304141</v>
+        <v>7303986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129930300</v>
+        <v>129930306</v>
       </c>
       <c r="B6" t="n">
-        <v>80221</v>
+        <v>80097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748211</v>
+        <v>747971</v>
       </c>
       <c r="R6" t="n">
-        <v>7303986</v>
+        <v>7304141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>129930308</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129930312</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129930302</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129930310</v>
       </c>
       <c r="B12" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129930304</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930307</v>
+        <v>129930311</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747938</v>
+        <v>748018</v>
       </c>
       <c r="R3" t="n">
-        <v>7304142</v>
+        <v>7304181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930311</v>
+        <v>129930307</v>
       </c>
       <c r="B4" t="n">
-        <v>80222</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748018</v>
+        <v>747938</v>
       </c>
       <c r="R4" t="n">
-        <v>7304181</v>
+        <v>7304142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129930300</v>
       </c>
       <c r="B5" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129930306</v>
       </c>
       <c r="B6" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129930308</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129930312</v>
       </c>
       <c r="B10" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129930302</v>
       </c>
       <c r="B11" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129930310</v>
       </c>
       <c r="B12" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129930304</v>
       </c>
       <c r="B13" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930307</v>
+        <v>129930311</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747938</v>
+        <v>748018</v>
       </c>
       <c r="R3" t="n">
-        <v>7304142</v>
+        <v>7304181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930311</v>
+        <v>129930307</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748018</v>
+        <v>747938</v>
       </c>
       <c r="R4" t="n">
-        <v>7304181</v>
+        <v>7304142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930311</v>
+        <v>129930307</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748018</v>
+        <v>747938</v>
       </c>
       <c r="R3" t="n">
-        <v>7304181</v>
+        <v>7304142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930307</v>
+        <v>129930311</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>80314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747938</v>
+        <v>748018</v>
       </c>
       <c r="R4" t="n">
-        <v>7304142</v>
+        <v>7304181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129930300</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129930306</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129930308</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129930309</v>
       </c>
       <c r="B9" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129930312</v>
       </c>
       <c r="B10" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129930302</v>
       </c>
       <c r="B11" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129930310</v>
       </c>
       <c r="B12" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129930304</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>129930313</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930307</v>
+        <v>129930312</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747938</v>
+        <v>748120</v>
       </c>
       <c r="R3" t="n">
-        <v>7304142</v>
+        <v>7304155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129930311</v>
+        <v>129930304</v>
       </c>
       <c r="B4" t="n">
-        <v>80314</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748018</v>
+        <v>748214</v>
       </c>
       <c r="R4" t="n">
-        <v>7304181</v>
+        <v>7303998</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129930300</v>
+        <v>129930306</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748211</v>
+        <v>747971</v>
       </c>
       <c r="R5" t="n">
-        <v>7303986</v>
+        <v>7304141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129930306</v>
+        <v>94729895</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747971</v>
+        <v>748086</v>
       </c>
       <c r="R6" t="n">
-        <v>7304141</v>
+        <v>7304205</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,17 +1168,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs inventering.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129930308</v>
+        <v>129930302</v>
       </c>
       <c r="B7" t="n">
-        <v>80314</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747939</v>
+        <v>748212</v>
       </c>
       <c r="R7" t="n">
-        <v>7304141</v>
+        <v>7303988</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>129930305</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129930309</v>
+        <v>129930307</v>
       </c>
       <c r="B9" t="n">
-        <v>97797</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>747930</v>
+        <v>747938</v>
       </c>
       <c r="R9" t="n">
-        <v>7304228</v>
+        <v>7304142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129930312</v>
+        <v>129930314</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748120</v>
+        <v>748320</v>
       </c>
       <c r="R10" t="n">
-        <v>7304155</v>
+        <v>7304047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,32 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129930302</v>
+        <v>129930300</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748212</v>
+        <v>748211</v>
       </c>
       <c r="R11" t="n">
-        <v>7303988</v>
+        <v>7303986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129930310</v>
+        <v>129930308</v>
       </c>
       <c r="B12" t="n">
-        <v>80320</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>748017</v>
+        <v>747939</v>
       </c>
       <c r="R12" t="n">
-        <v>7304184</v>
+        <v>7304141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129930304</v>
+        <v>129930311</v>
       </c>
       <c r="B13" t="n">
-        <v>79799</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>748214</v>
+        <v>748018</v>
       </c>
       <c r="R13" t="n">
-        <v>7303998</v>
+        <v>7304181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,6 +1944,218 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129930310</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>748017</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7304184</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129930309</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>747930</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7304228</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49843-2021 artfynd.xlsx
+++ b/artfynd/A 49843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930304</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930306</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94729895</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930302</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930305</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930307</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930314</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930300</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930311</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930310</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,8 +2226,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930309</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>